--- a/PPP_empirical_reinforcement_bundle_20260416_unified_v3/02_leave_one_province_out_jackknife/tables/leave_one_province_out_stability_summary.xlsx
+++ b/PPP_empirical_reinforcement_bundle_20260416_unified_v3/02_leave_one_province_out_jackknife/tables/leave_one_province_out_stability_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,10 +506,10 @@
         <v>0.0003845468522075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.266830239314566</v>
+        <v>0.2668302393145768</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4345081870376275</v>
+        <v>0.4345081870376022</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.08879746543807482</v>
+        <v>0.08879746543806405</v>
       </c>
     </row>
     <row r="3">
@@ -547,10 +547,10 @@
         <v>7.899841080299854e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4661525164563906</v>
+        <v>-0.4661525164563604</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2323783209330787</v>
+        <v>-0.232378320933089</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.1698991651596306</v>
+        <v>0.1698991651596203</v>
       </c>
     </row>
     <row r="4">
@@ -588,10 +588,10 @@
         <v>0.2125593654167483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2139394433788684</v>
+        <v>0.213939443378858</v>
       </c>
       <c r="G4" t="n">
-        <v>1.486312005015742</v>
+        <v>1.4863120050158</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.9610150694203422</v>
+        <v>0.9610150694204008</v>
       </c>
     </row>
   </sheetData>
